--- a/artfynd/A 13606-2022 artfynd.xlsx
+++ b/artfynd/A 13606-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13606-2022 artfynd.xlsx
+++ b/artfynd/A 13606-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>58965318</v>
       </c>
       <c r="B2" t="n">
-        <v>57587</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -739,10 +734,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435297.1185094903</v>
+        <v>435297</v>
       </c>
       <c r="R2" t="n">
-        <v>6509278.784506156</v>
+        <v>6509279</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,19 +767,9 @@
           <t>2016-04-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-04-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -811,15 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114628693</v>
+        <v>114628691</v>
       </c>
       <c r="B3" t="n">
-        <v>58086</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,26 +807,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -854,7 +834,11 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
@@ -898,12 +882,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,15 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114628695</v>
+        <v>114628693</v>
       </c>
       <c r="B4" t="n">
-        <v>58050</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,16 +926,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208245</v>
+        <v>208242</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -966,7 +945,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -976,7 +955,11 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>i lekdräkt</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1047,15 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114628691</v>
+        <v>114628695</v>
       </c>
       <c r="B5" t="n">
-        <v>58089</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,26 +1041,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100141</v>
+        <v>208245</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1090,17 +1068,9 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>i lekdräkt</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1138,12 +1108,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 13606-2022 artfynd.xlsx
+++ b/artfynd/A 13606-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58965318</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114628691</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1027,6 +1042,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114628693</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,8 +1158,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114628695</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>